--- a/data/trans_dic/P1410-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1410-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,14</t>
+          <t>2,22; 4,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,81</t>
+          <t>2,94; 6,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,38</t>
+          <t>4,2; 7,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,02</t>
+          <t>2,99; 6,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,53</t>
+          <t>3,28; 6,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,63</t>
+          <t>4,44; 8,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,8</t>
+          <t>4,11; 6,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,41</t>
+          <t>3,3; 5,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,21</t>
+          <t>3,09; 5,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,89</t>
+          <t>4,18; 6,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,57</t>
+          <t>4,52; 6,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,94</t>
+          <t>3,15; 5,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,18</t>
+          <t>2,8; 5,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,19</t>
+          <t>2,82; 5,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,23</t>
+          <t>3,39; 5,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,42</t>
+          <t>2,76; 5,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,65</t>
+          <t>3,12; 5,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,55</t>
+          <t>2,31; 4,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,52</t>
+          <t>3,52; 5,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,05</t>
+          <t>3,22; 5,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,09</t>
+          <t>3,22; 5,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,49</t>
+          <t>2,86; 4,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,88</t>
+          <t>3,86; 5,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,25</t>
+          <t>3,67; 7,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,25</t>
+          <t>2,33; 5,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,59</t>
+          <t>2,73; 5,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,66</t>
+          <t>4,49; 7,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,65</t>
+          <t>3,2; 6,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,34</t>
+          <t>1,79; 4,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,4</t>
+          <t>3,08; 6,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,85</t>
+          <t>2,46; 4,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,39</t>
+          <t>3,9; 6,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,27</t>
+          <t>2,39; 4,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,39</t>
+          <t>3,28; 5,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,43</t>
+          <t>3,82; 5,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,26</t>
+          <t>3,52; 6,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,0</t>
+          <t>3,26; 5,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,27</t>
+          <t>2,15; 4,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,2</t>
+          <t>4,49; 7,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,83</t>
+          <t>1,81; 3,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,13</t>
+          <t>3,41; 5,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,96</t>
+          <t>3,17; 5,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,29</t>
+          <t>3,64; 5,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,5</t>
+          <t>2,89; 4,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,58</t>
+          <t>3,72; 5,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,83</t>
+          <t>2,98; 4,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 5,78</t>
+          <t>4,27; 5,83</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,34</t>
+          <t>3,91; 5,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,49</t>
+          <t>3,24; 4,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,42</t>
+          <t>3,15; 4,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,9</t>
+          <t>4,71; 6,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,46</t>
+          <t>3,15; 4,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,92</t>
+          <t>3,54; 4,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,3</t>
+          <t>3,8; 5,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,71</t>
+          <t>3,84; 4,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,66</t>
+          <t>3,71; 4,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,51</t>
+          <t>3,58; 4,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 4,65</t>
+          <t>3,68; 4,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,11</t>
+          <t>4,46; 5,35</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>39234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35402</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71167</t>
+          <t>76988</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18886; 38881</t>
+          <t>18852; 38838</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15869; 36185</t>
+          <t>15641; 34509</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18859; 39236</t>
+          <t>19841; 40754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26851; 46773</t>
+          <t>28943; 50377</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19806; 41428</t>
+          <t>20607; 41607</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22827; 45542</t>
+          <t>22831; 44860</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31638; 58070</t>
+          <t>29850; 58125</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27256; 45935</t>
+          <t>30133; 49475</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45210; 74843</t>
+          <t>45581; 74632</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43570; 73000</t>
+          <t>43209; 72192</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56195; 92880</t>
+          <t>56289; 90479</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58702; 85984</t>
+          <t>64347; 94234</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43849</t>
+          <t>47650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>47290</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86044</t>
+          <t>94940</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30588; 57124</t>
+          <t>30293; 55347</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28263; 52717</t>
+          <t>28552; 53492</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28629; 53086</t>
+          <t>28785; 52525</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23416; 62385</t>
+          <t>35578; 61366</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26397; 52530</t>
+          <t>26696; 52027</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32393; 58047</t>
+          <t>32063; 58818</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22943; 47476</t>
+          <t>24058; 48522</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33808; 52857</t>
+          <t>37675; 58159</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62481; 97539</t>
+          <t>62121; 99051</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67418; 104107</t>
+          <t>65847; 103359</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58366; 92731</t>
+          <t>59040; 94502</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58236; 104863</t>
+          <t>81811; 114511</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44128</t>
+          <t>47829</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68478</t>
+          <t>75670</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26438; 49198</t>
+          <t>24897; 49066</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16656; 39812</t>
+          <t>17628; 39979</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20338; 42442</t>
+          <t>20760; 42166</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32222; 60884</t>
+          <t>35983; 63017</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22573; 45451</t>
+          <t>21907; 44361</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14345; 33718</t>
+          <t>13880; 34653</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25371; 50206</t>
+          <t>24210; 50324</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11186; 35868</t>
+          <t>19944; 38365</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52577; 87112</t>
+          <t>53161; 86616</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36464; 65475</t>
+          <t>36637; 66021</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50000; 83253</t>
+          <t>50695; 82021</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46207; 88816</t>
+          <t>61519; 95818</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53218</t>
+          <t>56251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45647</t>
+          <t>50144</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98865</t>
+          <t>106395</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33139; 59015</t>
+          <t>33155; 56780</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30963; 56821</t>
+          <t>30904; 55840</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20284; 40036</t>
+          <t>20154; 41101</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42958; 66771</t>
+          <t>44498; 70072</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19193; 39790</t>
+          <t>18764; 38561</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37008; 64530</t>
+          <t>35859; 62864</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33652; 62254</t>
+          <t>33122; 60840</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33821; 57793</t>
+          <t>40710; 62437</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56141; 89102</t>
+          <t>57268; 87864</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75116; 111592</t>
+          <t>74338; 111252</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59198; 95784</t>
+          <t>58961; 94959</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80647; 116710</t>
+          <t>90048; 122843</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176960</t>
+          <t>190965</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>324555</t>
+          <t>353993</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>128507; 175060</t>
+          <t>128162; 176137</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>111254; 153947</t>
+          <t>111168; 157690</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>105577; 150123</t>
+          <t>106988; 151519</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132194; 204021</t>
+          <t>166361; 216189</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>105205; 150696</t>
+          <t>106550; 149062</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>126734; 174749</t>
+          <t>125933; 174392</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>134252; 187856</t>
+          <t>134684; 187085</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>124331; 172075</t>
+          <t>143315; 183498</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>244433; 310370</t>
+          <t>246647; 309740</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>248326; 314820</t>
+          <t>250073; 315456</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>255287; 322397</t>
+          <t>255624; 324470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>279511; 363416</t>
+          <t>323764; 388032</t>
         </is>
       </c>
     </row>
